--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Pessoa</t>
   </si>
@@ -30,22 +30,16 @@
     <t>Vencimento</t>
   </si>
   <si>
-    <t>Erika</t>
-  </si>
-  <si>
-    <t>5521996419954</t>
-  </si>
-  <si>
-    <t>Paio</t>
-  </si>
-  <si>
-    <t>Manho</t>
-  </si>
-  <si>
-    <t>5521987674266</t>
-  </si>
-  <si>
-    <t>5522988433392</t>
+    <t>Pessoa1</t>
+  </si>
+  <si>
+    <t>Pessoa2</t>
+  </si>
+  <si>
+    <t>Pessoa3</t>
+  </si>
+  <si>
+    <t>5521999999999</t>
   </si>
 </sst>
 </file>
@@ -84,9 +78,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -407,33 +400,33 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45698</v>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46428</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45698</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46428</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45698</v>
+      <c r="C4" s="1">
+        <v>46428</v>
       </c>
     </row>
   </sheetData>
